--- a/stories/arbres/TREE-AUT-005.xlsx
+++ b/stories/arbres/TREE-AUT-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la ferme, avec maman. Papa ouvre la porte. C'est le matin. Il y a plusieurs étapes. Maman dit : on fait une étape après l'autre.</t>
+          <t>Léa est à la ferme, avec maman. Papa ouvre la porte. C'est le matin. Il y a plusieurs étapes. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,12 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est à la ferme, avec maman. Papa ouvre la porte. C'est le matin. Il y a plusieurs étapes.
+maman|On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1510,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1511,7 +1539,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le ballon rouge. Maman dit : d'abord on s'habille. Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
+          <t>Léa prend le ballon rouge. D'abord on s'habille. Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1649,6 +1677,13 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prend le ballon rouge.
+maman|D'abord on s'habille.
+narrateur|Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1864,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On fait une étape après l'autre ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2037,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Une étape après l'autre. Léa respire. Maman est là. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2187,6 +2232,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2211,7 +2261,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à Tom. Puis elle se lave les mains. Une étape après l'autre. Maman dit : ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+          <t>Léa a posé le ballon. Elle dit bonjour à Tom. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2349,6 +2399,12 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à Tom. Puis elle se lave les mains. Une étape après l'autre.
+maman|Ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2535,6 +2591,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2697,6 +2758,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le ballon rouge. Puis Tom. Puis le matin. On rit un peu. Léa range le ballon rouge dans sa tête, comme un souvenir. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2859,6 +2925,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3021,6 +3092,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Léa caresse le doudou. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3183,6 +3259,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3345,6 +3426,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de le ballon rouge. Et de Tom. Et de le soir. Un ballon s'immobilise. Léa enfile ses chaussons. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3507,6 +3593,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3531,7 +3622,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à une amie Léa. Puis elle se lave les mains. Une étape après l'autre. Maman dit : ensuite, le goûter. Maman dit : je suis là. On fait une étape après l'autre.</t>
+          <t>Léa a posé le ballon. Elle dit bonjour à une amie Léa. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3669,6 +3760,13 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à une amie Léa. Puis elle se lave les mains. Une étape après l'autre.
+maman|Ensuite, le goûter.
+maman|Je suis là. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3855,6 +3953,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4017,6 +4120,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Léa s'arrête. On range un objet. Léa pose sa tête un moment. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4179,6 +4287,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4341,6 +4454,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range Léa. après la sieste reste près de le ballon rouge. La couverture est douce. Léa boit une gorgée d'eau. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4503,6 +4621,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4527,7 +4650,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4665,6 +4788,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4827,6 +4955,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4851,7 +4984,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à Sami. Puis elle se lave les mains. Une étape après l'autre. Maman dit : ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
+          <t>Léa a posé le ballon. Elle dit bonjour à Sami. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -4989,6 +5122,12 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à Sami. Puis elle se lave les mains. Une étape après l'autre.
+maman|Ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5175,6 +5314,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5337,6 +5481,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le matin. Sami est rangé. le ballon rouge est fini. On se tient la main. Léa s'assoit près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5499,6 +5648,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5661,6 +5815,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Léa pose Sami. le ballon rouge est derrière. La lumière est claire. Léa plie un pull. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5823,6 +5982,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5985,6 +6149,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre le soir. Maman a vu le ballon rouge. Et Sami. Un vélo passe au loin. Léa prend la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6147,6 +6316,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6171,7 +6345,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le seau bleu. Maman dit : d'abord on déjeune. Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
+          <t>Léa prend le seau bleu. D'abord on déjeune. Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6309,6 +6483,13 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prend le seau bleu.
+maman|D'abord on déjeune.
+narrateur|Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6666,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|On fait tout en même temps ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6839,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Une étape après l'autre. Léa retient le geste. Maman sourit. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6843,6 +7034,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -6867,7 +7063,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le seau. Elle suit Tom vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman dit : je suis là. On fait une étape après l'autre.</t>
+          <t>Léa a posé le seau. Elle suit Tom vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7005,6 +7201,12 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le seau. Elle suit Tom vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide.
+maman|Je suis là. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7191,6 +7393,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7353,6 +7560,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le seau bleu. Puis Tom. Puis le matin. Un linge sèche à l'air. Léa souffle, puis sourit à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7515,6 +7727,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7677,6 +7894,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le sol est un peu froid. Léa pose Tom à sa place. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7839,6 +8061,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7863,7 +8090,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Léa se souvient de le seau bleu. Et de Tom. Et de le soir. Ça sent le pain chaud. Léa dit : j'ai appris. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Léa se souvient de le seau bleu. Et de Tom. Et de le soir. Ça sent le pain chaud. J'ai appris. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8001,6 +8228,13 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de le seau bleu. Et de Tom. Et de le soir. Ça sent le pain chaud.
+enfant-f|J'ai appris. On fait une étape après l'autre. On fait l'étape dite.
+narrateur|Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8163,6 +8397,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8325,6 +8564,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le seau. Elle suit son amie Léa vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman reste tout près. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8511,6 +8755,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8673,6 +8922,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Léa s'arrête. On attend son tour. Léa dit merci à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8835,6 +9089,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8997,6 +9256,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range Léa. après la sieste reste près de le seau bleu. Une chaussette est encore sablée. Léa sourit. Maman sourit aussi. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9159,6 +9423,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9183,7 +9452,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9321,6 +9590,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9483,6 +9757,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9645,6 +9924,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le seau. Elle suit Sami vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9831,6 +10115,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9993,6 +10282,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le matin. Sami est rangé. le seau bleu est fini. L'eau coule, tout petit bruit. Léa raccroche un linge. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10155,6 +10449,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10317,6 +10616,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Léa pose Sami. le seau bleu est derrière. Le vent est doux. Léa montre après la sieste à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10479,6 +10783,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10641,6 +10950,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre le soir. Maman a vu le seau bleu. Et Sami. Les chaussures font toc toc. Léa ferme la porte, tout doux. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10803,6 +11117,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10827,7 +11146,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le doudou. Maman dit : d'abord on prépare le sac. Léa pose le doudou. Elle met le gobelet. Une étape après l'autre. Papa dit : ensuite, le doudou.</t>
+          <t>Léa prend le doudou. D'abord on prépare le sac. Léa pose le doudou. Elle met le gobelet. Une étape après l'autre. Ensuite, le doudou.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10965,6 +11284,14 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Léa prend le doudou.
+maman|D'abord on prépare le sac.
+narrateur|Léa pose le doudou. Elle met le gobelet. Une étape après l'autre.
+papa|Ensuite, le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11145,6 +11472,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Quelle étape maintenant ?</t>
         </is>
       </c>
     </row>
@@ -11313,6 +11645,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Une étape après l'autre. Léa hoche la tête. On continue, avec maman. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11501,6 +11838,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
     </row>
@@ -11665,6 +12007,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le doudou. Avec Tom, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman reste tout près. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11851,6 +12198,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12013,6 +12365,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a choisi le doudou. Puis Tom. Puis le matin. On entend un oiseau. Léa range encore un peu, près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12175,6 +12532,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12337,6 +12699,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Papa n'est pas loin. Léa les rejoint. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12499,6 +12866,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12661,6 +13033,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa se souvient de le doudou. Et de Tom. Et de le soir. On dit merci. Léa répète tout bas le geste. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12823,6 +13200,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12985,6 +13367,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le doudou. Avec son amie Léa, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13171,6 +13558,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13333,6 +13725,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Léa s'arrête. Un chat miaule une fois. Léa tend le matin à papa. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13495,6 +13892,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13657,6 +14059,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa range Léa. après la sieste reste près de le doudou. Il y a des miettes sur la table. Léa marche près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13819,6 +14226,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13843,7 +14255,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -13981,6 +14393,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14143,6 +14560,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14167,7 +14589,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le doudou. Avec Sami, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman dit : je suis là. On fait une étape après l'autre.</t>
+          <t>Léa a posé le doudou. Avec Sami, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14305,6 +14727,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a posé le doudou. Avec Sami, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou.
+maman|Je suis là. On fait une étape après l'autre.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14491,6 +14919,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14653,6 +15086,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa rejoint le matin. Sami est rangé. le doudou est fini. Une feuille tombe. Léa chuchote : c'est fini. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14815,6 +15253,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14977,6 +15420,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Près de après la sieste. Léa pose Sami. le doudou est derrière. Un galet est encore chaud. Léa écoute maman encore une fois. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15139,6 +15587,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15301,6 +15754,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa montre le soir. Maman a vu le doudou. Et Sami. Une tasse cliquette. Léa range la tasse. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15463,6 +15921,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15481,7 +15944,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15512,6 +15975,13 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-005.xlsx
+++ b/stories/arbres/TREE-AUT-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1324,6 +1329,7 @@
 maman|On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1515,6 +1521,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1684,6 +1691,7 @@
 narrateur|Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1871,6 +1879,7 @@
           <t>narrateur|On fait une étape après l'autre ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2042,6 +2051,7 @@
           <t>narrateur|Oui. Une étape après l'autre. Léa respire. Maman est là. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2237,6 +2247,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
 maman|Ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2596,6 +2608,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2763,6 +2776,7 @@
           <t>narrateur|Léa a choisi le ballon rouge. Puis Tom. Puis le matin. On rit un peu. Léa range le ballon rouge dans sa tête, comme un souvenir. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2930,6 +2944,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3097,6 +3112,7 @@
           <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Léa caresse le doudou. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3264,6 +3280,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3431,6 +3448,7 @@
           <t>narrateur|Léa se souvient de le ballon rouge. Et de Tom. Et de le soir. Un ballon s'immobilise. Léa enfile ses chaussons. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3598,6 +3616,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3767,6 +3786,7 @@
 maman|Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3958,6 +3978,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4125,6 +4146,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Léa s'arrête. On range un objet. Léa pose sa tête un moment. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4292,6 +4314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4459,6 +4482,7 @@
           <t>narrateur|Léa range Léa. après la sieste reste près de le ballon rouge. La couverture est douce. Léa boit une gorgée d'eau. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4626,6 +4650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4793,6 +4818,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4960,6 +4986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5128,6 +5155,7 @@
 maman|Ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5319,6 +5347,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5486,6 +5515,7 @@
           <t>narrateur|Léa rejoint le matin. Sami est rangé. le ballon rouge est fini. On se tient la main. Léa s'assoit près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5653,6 +5683,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5820,6 +5851,7 @@
           <t>narrateur|Près de après la sieste. Léa pose Sami. le ballon rouge est derrière. La lumière est claire. Léa plie un pull. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5987,6 +6019,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6154,6 +6187,7 @@
           <t>narrateur|Léa montre le soir. Maman a vu le ballon rouge. Et Sami. Un vélo passe au loin. Léa prend la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6321,6 +6355,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6490,6 +6525,7 @@
 narrateur|Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6673,6 +6709,7 @@
           <t>narrateur|On fait tout en même temps ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6844,6 +6881,7 @@
           <t>narrateur|Oui. Une étape après l'autre. Léa retient le geste. Maman sourit. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7039,6 +7077,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7207,6 +7246,7 @@
 maman|Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7398,6 +7438,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7565,6 +7606,7 @@
           <t>narrateur|Léa a choisi le seau bleu. Puis Tom. Puis le matin. Un linge sèche à l'air. Léa souffle, puis sourit à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7732,6 +7774,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7899,6 +7942,7 @@
           <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le sol est un peu froid. Léa pose Tom à sa place. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8066,6 +8110,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8235,6 +8280,7 @@
 narrateur|Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8402,6 +8448,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8569,6 +8616,7 @@
           <t>narrateur|Léa a posé le seau. Elle suit son amie Léa vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman reste tout près. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8760,6 +8808,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8927,6 +8976,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Léa s'arrête. On attend son tour. Léa dit merci à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9094,6 +9144,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9261,6 +9312,7 @@
           <t>narrateur|Léa range Léa. après la sieste reste près de le seau bleu. Une chaussette est encore sablée. Léa sourit. Maman sourit aussi. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9428,6 +9480,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9595,6 +9648,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9762,6 +9816,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9929,6 +9984,7 @@
           <t>narrateur|Léa a posé le seau. Elle suit Sami vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10120,6 +10176,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10287,6 +10344,7 @@
           <t>narrateur|Léa rejoint le matin. Sami est rangé. le seau bleu est fini. L'eau coule, tout petit bruit. Léa raccroche un linge. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10454,6 +10512,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10621,6 +10680,7 @@
           <t>narrateur|Près de après la sieste. Léa pose Sami. le seau bleu est derrière. Le vent est doux. Léa montre après la sieste à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10788,6 +10848,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10955,6 +11016,7 @@
           <t>narrateur|Léa montre le soir. Maman a vu le seau bleu. Et Sami. Les chaussures font toc toc. Léa ferme la porte, tout doux. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11122,6 +11184,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11292,6 +11355,7 @@
 papa|Ensuite, le doudou.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11479,6 +11543,7 @@
           <t>narrateur|Quelle étape maintenant ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11650,6 +11715,7 @@
           <t>narrateur|Oui. Une étape après l'autre. Léa hoche la tête. On continue, avec maman. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11845,6 +11911,7 @@
           <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12012,6 +12079,7 @@
           <t>narrateur|Léa a posé le doudou. Avec Tom, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman reste tout près. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12203,6 +12271,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12370,6 +12439,7 @@
           <t>narrateur|Léa a choisi le doudou. Puis Tom. Puis le matin. On entend un oiseau. Léa range encore un peu, près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12537,6 +12607,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12704,6 +12775,7 @@
           <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Papa n'est pas loin. Léa les rejoint. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12871,6 +12943,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13038,6 +13111,7 @@
           <t>narrateur|Léa se souvient de le doudou. Et de Tom. Et de le soir. On dit merci. Léa répète tout bas le geste. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13205,6 +13279,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13372,6 +13447,7 @@
           <t>narrateur|Léa a posé le doudou. Avec son amie Léa, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13563,6 +13639,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13730,6 +13807,7 @@
           <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Léa s'arrête. Un chat miaule une fois. Léa tend le matin à papa. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13897,6 +13975,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14064,6 +14143,7 @@
           <t>narrateur|Léa range Léa. après la sieste reste près de le doudou. Il y a des miettes sur la table. Léa marche près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14231,6 +14311,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14398,6 +14479,7 @@
           <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14565,6 +14647,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14733,6 +14816,7 @@
 maman|Je suis là. On fait une étape après l'autre.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14924,6 +15008,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15091,6 +15176,7 @@
           <t>narrateur|Léa rejoint le matin. Sami est rangé. le doudou est fini. Une feuille tombe. Léa chuchote : c'est fini. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15258,6 +15344,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15425,6 +15512,7 @@
           <t>narrateur|Près de après la sieste. Léa pose Sami. le doudou est derrière. Un galet est encore chaud. Léa écoute maman encore une fois. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15592,6 +15680,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15759,6 +15848,7 @@
           <t>narrateur|Léa montre le soir. Maman a vu le doudou. Et Sami. Une tasse cliquette. Léa range la tasse. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15926,6 +16016,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15944,7 +16035,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15982,6 +16073,20 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15996,7 +16101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16183,6 +16288,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-005.xlsx
+++ b/stories/arbres/TREE-AUT-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Enchaîner le matin — à la ferme</t>
+          <t>Le coq et les bottes de Raphaël</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël se lève à la ferme. Il veut voir les bêtes. Pour y aller, il fait une étape après l'autre : s'habiller, déjeuner, bottes, puis le chat, le chien ou la poule.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la ferme, avec maman. Papa ouvre la porte. C'est le matin. Il y a plusieurs étapes. On fait une étape après l'autre.</t>
+          <t>Un coq chante derrière la grange. L'herbe brille, encore mouillée. La petite maison sent le foin chaud. Un volet bleu bouge tout doux. Les bottes de papa attendent près de la porte. Dans la cuisine, le lait fume. Le lait est prêt, Raphaël. Tu as entendu le coq ? Oui, papa. Le bois du plancher est un peu froid. Un rayon pose une barre jaune. En ce moment, Raphaël est dans la cuisine. Il tient son doudou contre sa joue. Il a envie d'aller voir les bêtes. D'abord on s'habille. Ensuite on déjeune. Une étape après l'autre, mon grand. Une étape après l'autre. Raphaël hoche la tête. Tu es prêt ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,11 +1337,34 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Léa est à la ferme, avec maman. Papa ouvre la porte. C'est le matin. Il y a plusieurs étapes.
-maman|On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Un coq chante derrière la grange.
+narrateur|L'herbe brille, encore mouillée.
+narrateur|La petite maison sent le foin chaud.
+narrateur|Un volet bleu bouge tout doux.
+narrateur|Les bottes de papa attendent près de la porte.
+narrateur|Dans la cuisine, le lait fume.
+maman|Le lait est prêt, Raphaël.
+papa|Tu as entendu le coq ?
+enfant-m|Oui, papa.
+narrateur|Le bois du plancher est un peu froid.
+narrateur|Un rayon pose une barre jaune.
+narrateur|En ce moment, Raphaël est dans la cuisine.
+narrateur|Il tient son doudou contre sa joue.
+narrateur|Il a envie d'aller voir les bêtes.
+papa|D'abord on s'habille.
+papa|Ensuite on déjeune.
+maman|Une étape après l'autre, mon grand.
+enfant-m|Une étape après l'autre.
+narrateur|Raphaël hoche la tête.
+maman|Tu es prêt ?
+enfant-m|Oui, maman.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>coq,porte,lait</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1354,7 +1389,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>Qu'est-ce que Raphaël prend ? Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1518,7 +1553,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+          <t>narrateur|Qu'est-ce que Raphaël prend ?
+maman|Le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1546,7 +1582,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le ballon rouge. D'abord on s'habille. Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
+          <t>Raphaël prend le ballon rouge. Le ballon est lisse, un peu tiède. D'abord on s'habille. Raphaël pose le ballon sur la chaise. Il enfile le pull de laine. Le pull gratte un tout petit peu. Tu as mis ton pull ? Oui, papa. Bravo, Raphaël. Tu as fait du bon travail. Papa ouvre les volets. La lumière tombe sur le plancher. Une étape après l'autre. Raphaël touche encore le ballon. Il attend la suite.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1686,12 +1722,28 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Léa prend le ballon rouge.
+          <t>narrateur|Raphaël prend le ballon rouge.
+narrateur|Le ballon est lisse, un peu tiède.
 maman|D'abord on s'habille.
-narrateur|Léa pose le ballon. Elle met le pull. Une étape après l'autre. Papa ouvre les volets.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+narrateur|Raphaël pose le ballon sur la chaise.
+narrateur|Il enfile le pull de laine.
+narrateur|Le pull gratte un tout petit peu.
+papa|Tu as mis ton pull ?
+enfant-m|Oui, papa.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+narrateur|Papa ouvre les volets.
+narrateur|La lumière tombe sur le plancher.
+maman|Une étape après l'autre.
+narrateur|Raphaël touche encore le ballon.
+narrateur|Il attend la suite.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>volet,pull</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1904,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Une étape après l'autre. Léa respire. Maman est là. On fait une étape après l'autre.</t>
+          <t>Oui. Une étape après l'autre. Raphaël respire, tout calme. Bravo, Raphaël. Tu as fait du bon travail. On continue, tout doux. Oui, maman.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2048,7 +2100,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Une étape après l'autre. Léa respire. Maman est là. On fait une étape après l'autre.</t>
+          <t>narrateur|Oui.
+maman|Une étape après l'autre.
+narrateur|Raphaël respire, tout calme.
+papa|Bravo, Raphaël.
+papa|Tu as fait du bon travail.
+maman|On continue, tout doux.
+enfant-m|Oui, maman.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2076,7 +2134,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va voir qui ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2244,7 +2302,8 @@
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va voir qui ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2272,7 +2331,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à Tom. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le ballon. Le chat dort dans la paille. D'abord on se lave les mains. L'eau est tiède, un peu savon. Ensuite, on dit bonjour au chat. Raphaël caresse le chat, tout doux. Le poil est chaud. Il ronronne. Tu as lavé tes mains ? Oui, papa. Bravo. Une étape après l'autre. Le ballon attend à sa place.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2412,11 +2471,26 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à Tom. Puis elle se lave les mains. Une étape après l'autre.
-maman|Ensuite, le goûter. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le ballon.
+narrateur|Le chat dort dans la paille.
+papa|D'abord on se lave les mains.
+narrateur|L'eau est tiède, un peu savon.
+maman|Ensuite, on dit bonjour au chat.
+narrateur|Raphaël caresse le chat, tout doux.
+narrateur|Le poil est chaud.
+enfant-m|Il ronronne.
+papa|Tu as lavé tes mains ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le ballon attend à sa place.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>eau,chat</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2441,7 +2515,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2605,7 +2679,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2633,7 +2708,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le ballon rouge. Puis Tom. Puis le matin. On rit un peu. Léa range le ballon rouge dans sa tête, comme un souvenir. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>C'est le matin. Raphaël a le ballon rouge. Le chat se frotte contre sa jambe. D'abord le ballon dans la caisse. Raphaël pose le ballon, tout doux. Ensuite on donne le lait au chat. Le chat lape, tout petit bruit. Il a soif. Bravo, Raphaël. Tu as fait l'étape dite. Une étape après l'autre. Le soleil chauffe la paille. Merci, maman. Merci, papa.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2773,10 +2848,27 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le ballon rouge. Puis Tom. Puis le matin. On rit un peu. Léa range le ballon rouge dans sa tête, comme un souvenir. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|Raphaël a le ballon rouge.
+narrateur|Le chat se frotte contre sa jambe.
+maman|D'abord le ballon dans la caisse.
+narrateur|Raphaël pose le ballon, tout doux.
+papa|Ensuite on donne le lait au chat.
+narrateur|Le chat lape, tout petit bruit.
+enfant-m|Il a soif.
+maman|Bravo, Raphaël.
+maman|Tu as fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Le soleil chauffe la paille.
+enfant-m|Merci, maman.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2801,7 +2893,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2941,7 +3033,13 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chat.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2969,7 +3067,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Léa s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Léa caresse le doudou. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, la maison est calme. Le chat est sur la couverture. Le ballon rouge attend sous le banc. D'abord on range le ballon. Raphaël le glisse dans la caisse. Ensuite on met les chaussons. Les chaussons sont chauds, un peu mous. Tu as mis tes chaussons ? Oui, maman. Bravo. Une étape après l'autre. Le chat ronronne tout près. Merci, papa.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3109,10 +3207,26 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. On écoute jusqu'au bout. Léa caresse le doudou. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|Après la sieste, la maison est calme.
+narrateur|Le chat est sur la couverture.
+narrateur|Le ballon rouge attend sous le banc.
+papa|D'abord on range le ballon.
+narrateur|Raphaël le glisse dans la caisse.
+maman|Ensuite on met les chaussons.
+narrateur|Les chaussons sont chauds, un peu mous.
+maman|Tu as mis tes chaussons ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+narrateur|Le chat ronronne tout près.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3137,7 +3251,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3277,7 +3391,13 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chat.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3305,7 +3425,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Léa se souvient de le ballon rouge. Et de Tom. Et de le soir. Un ballon s'immobilise. Léa enfile ses chaussons. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, une lampe est allumée. Le chat se couche près du poêle. Raphaël tient encore le ballon rouge. D'abord le ballon dans la boîte. Raphaël le pose, sans le faire rouler. Ensuite les chaussons. Raphaël enfile les chaussons, un pied, puis l'autre. Tu as fait l'étape dite ? Oui, papa. Bravo, mon grand. Une étape après l'autre. La ferme devient toute douce. Merci, maman.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3445,10 +3565,26 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Léa se souvient de le ballon rouge. Et de Tom. Et de le soir. Un ballon s'immobilise. Léa enfile ses chaussons. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|Le soir, une lampe est allumée.
+narrateur|Le chat se couche près du poêle.
+narrateur|Raphaël tient encore le ballon rouge.
+maman|D'abord le ballon dans la boîte.
+narrateur|Raphaël le pose, sans le faire rouler.
+papa|Ensuite les chaussons.
+narrateur|Raphaël enfile les chaussons, un pied, puis l'autre.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui, papa.
+maman|Bravo, mon grand.
+maman|Une étape après l'autre.
+narrateur|La ferme devient toute douce.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3473,7 +3609,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3613,7 +3749,13 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chat.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3641,7 +3783,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à une amie Léa. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Je suis là. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le ballon. Le chien attend près de l'étable. D'abord les bottes. Raphaël enfile la botte gauche. Puis la botte droite. Ensuite, on dit bonjour au chien. Le chien remue la queue. Wouaf, tout doux. Tu as mis tes bottes ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Le ballon reste près de la porte.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3781,12 +3923,26 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à une amie Léa. Puis elle se lave les mains. Une étape après l'autre.
-maman|Ensuite, le goûter.
-maman|Je suis là. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le ballon.
+narrateur|Le chien attend près de l'étable.
+papa|D'abord les bottes.
+narrateur|Raphaël enfile la botte gauche.
+narrateur|Puis la botte droite.
+maman|Ensuite, on dit bonjour au chien.
+narrateur|Le chien remue la queue.
+enfant-m|Wouaf, tout doux.
+papa|Tu as mis tes bottes ?
+enfant-m|Oui, papa.
+papa|Bravo, Raphaël.
+papa|Une étape après l'autre.
+narrateur|Le ballon reste près de la porte.</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>bottes,chien</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3811,7 +3967,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3975,7 +4131,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -4003,7 +4160,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le ballon rouge. Léa s'arrête. On range un objet. Léa pose sa tête un moment. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin sent l'herbe mouillée. Le chien remue la queue. Raphaël tient le ballon rouge. D'abord on pose le ballon. Le ballon s'arrête contre le seau. Ensuite l'eau du chien. Raphaël pose la gamelle, tout doux. Il boit. Bravo, Raphaël. Tu as fait l'étape dite. Une étape après l'autre. Un oiseau chante sur la grange. Merci, papa.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4143,10 +4300,26 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le ballon rouge. Léa s'arrête. On range un objet. Léa pose sa tête un moment. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Le matin sent l'herbe mouillée.
+narrateur|Le chien remue la queue.
+narrateur|Raphaël tient le ballon rouge.
+papa|D'abord on pose le ballon.
+narrateur|Le ballon s'arrête contre le seau.
+maman|Ensuite l'eau du chien.
+narrateur|Raphaël pose la gamelle, tout doux.
+enfant-m|Il boit.
+papa|Bravo, Raphaël.
+papa|Tu as fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Un oiseau chante sur la grange.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,7 +4344,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4311,7 +4484,13 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chien.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4339,7 +4518,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Léa range Léa. après la sieste reste près de le ballon rouge. La couverture est douce. Léa boit une gorgée d'eau. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le chien dort à l'ombre. Le ballon rouge est sous le banc. D'abord on range le ballon. Raphaël le met dans le panier. Ensuite on dit bonjour au chien. Raphaël pose la main sur le poil chaud. Il est doux. Tu as rangé le ballon ? Oui, maman. Bravo. Une étape après l'autre. Le vent est doux dans la cour. Merci, maman.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4479,10 +4658,26 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Léa range Léa. après la sieste reste près de le ballon rouge. La couverture est douce. Léa boit une gorgée d'eau. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le chien dort à l'ombre.
+narrateur|Le ballon rouge est sous le banc.
+maman|D'abord on range le ballon.
+narrateur|Raphaël le met dans le panier.
+papa|Ensuite on dit bonjour au chien.
+narrateur|Raphaël pose la main sur le poil chaud.
+enfant-m|Il est doux.
+maman|Tu as rangé le ballon ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+narrateur|Le vent est doux dans la cour.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4507,7 +4702,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4647,7 +4842,13 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chien.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4675,7 +4876,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, les pattes du chien font toc toc. Raphaël ramène le ballon rouge. D'abord le ballon dans le panier. Le panier craque un peu. Ensuite on ferme la porte, tout doux. Raphaël pousse la porte avec papa. Tu as fait l'étape dite ? Oui. Bravo, Raphaël. Une étape après l'autre. La cour devient silencieuse. Merci, papa.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4815,10 +5016,25 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le ballon rouge reste dans le souvenir. Une pomme brille un peu. Léa essuie ses mains. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|Le soir, les pattes du chien font toc toc.
+narrateur|Raphaël ramène le ballon rouge.
+papa|D'abord le ballon dans le panier.
+narrateur|Le panier craque un peu.
+maman|Ensuite on ferme la porte, tout doux.
+narrateur|Raphaël pousse la porte avec papa.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui.
+maman|Bravo, Raphaël.
+maman|Une étape après l'autre.
+narrateur|La cour devient silencieuse.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4843,7 +5059,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4983,7 +5199,13 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chien.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -5011,7 +5233,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le ballon. Elle dit bonjour à Sami. Puis elle se lave les mains. Une étape après l'autre. Ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le ballon. La poule picore dans la cour. D'abord le manteau. Raphaël passe un bras, puis l'autre. Ensuite, on va voir la poule. La poule fait cot-cot. Cot-cot. Tu as mis ton manteau ? Oui, maman. Bravo. Une étape après l'autre. Le ballon reste sur le banc.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5151,11 +5373,25 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le ballon. Elle dit bonjour à Sami. Puis elle se lave les mains. Une étape après l'autre.
-maman|Ensuite, le goûter. Maman reste tout près. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le ballon.
+narrateur|La poule picore dans la cour.
+maman|D'abord le manteau.
+narrateur|Raphaël passe un bras, puis l'autre.
+papa|Ensuite, on va voir la poule.
+narrateur|La poule fait cot-cot.
+enfant-m|Cot-cot.
+maman|Tu as mis ton manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le ballon reste sur le banc.</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>manteau,poule</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5180,7 +5416,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5344,7 +5580,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5372,7 +5609,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le matin. Sami est rangé. le ballon rouge est fini. On se tient la main. Léa s'assoit près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, la poule picore près du seau. Raphaël a le ballon rouge sous le bras. D'abord le ballon sur le crochet. Raphaël le pose. Il ne roule plus. Ensuite un peu de grain. Le grain tombe, tout petit bruit. Cot-cot. Bravo. Tu as fait l'étape dite. Une étape après l'autre. Le soleil touche les plumes. Merci, maman.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5512,10 +5749,25 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le matin. Sami est rangé. le ballon rouge est fini. On se tient la main. Léa s'assoit près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Le matin, la poule picore près du seau.
+narrateur|Raphaël a le ballon rouge sous le bras.
+maman|D'abord le ballon sur le crochet.
+narrateur|Raphaël le pose. Il ne roule plus.
+papa|Ensuite un peu de grain.
+narrateur|Le grain tombe, tout petit bruit.
+enfant-m|Cot-cot.
+maman|Bravo.
+maman|Tu as fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Le soleil touche les plumes.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5540,7 +5792,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5680,7 +5932,13 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec la poule.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5708,7 +5966,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Léa pose Sami. le ballon rouge est derrière. La lumière est claire. Léa plie un pull. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, la cour est tiède. La poule se tient près du grillage. Le ballon rouge attend sur le banc. D'abord on range le ballon. Raphaël le met dans la caisse. Ensuite on regarde la poule, sans la presser. Raphaël reste près de maman. Tu as rangé le ballon ? Oui. Bravo, Raphaël. Une étape après l'autre. Merci, papa.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5848,10 +6106,25 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Léa pose Sami. le ballon rouge est derrière. La lumière est claire. Léa plie un pull. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|Après la sieste, la cour est tiède.
+narrateur|La poule se tient près du grillage.
+narrateur|Le ballon rouge attend sur le banc.
+papa|D'abord on range le ballon.
+narrateur|Raphaël le met dans la caisse.
+maman|Ensuite on regarde la poule, sans la presser.
+narrateur|Raphaël reste près de maman.
+maman|Tu as rangé le ballon ?
+enfant-m|Oui.
+papa|Bravo, Raphaël.
+papa|Une étape après l'autre.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5876,7 +6149,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6016,7 +6289,13 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec la poule.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6044,7 +6323,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Léa montre le soir. Maman a vu le ballon rouge. Et Sami. Un vélo passe au loin. Léa prend la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, la poule rentre au poulailler. Raphaël porte encore le ballon rouge. D'abord le ballon dans la boîte. Raphaël le pose, tout lentement. Ensuite on ferme le petit volet. Le volet fait un clac doux. Tu as fait l'étape dite ? Oui, papa. Bravo. Une étape après l'autre. La nuit arrive tout doux. Merci, maman.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6184,10 +6463,25 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Léa montre le soir. Maman a vu le ballon rouge. Et Sami. Un vélo passe au loin. Léa prend la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|Le soir, la poule rentre au poulailler.
+narrateur|Raphaël porte encore le ballon rouge.
+maman|D'abord le ballon dans la boîte.
+narrateur|Raphaël le pose, tout lentement.
+papa|Ensuite on ferme le petit volet.
+narrateur|Le volet fait un clac doux.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|La nuit arrive tout doux.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6212,7 +6506,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6352,7 +6646,13 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec la poule.
+narrateur|Il a posé le ballon rouge, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6380,7 +6680,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le seau bleu. D'abord on déjeune. Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
+          <t>Raphaël prend le seau bleu. Le seau fait un petit bruit de fer. D'abord on déjeune. Raphaël pose le seau près de la porte. Il s'assoit à la table de bois. Le lait est chaud dans le bol. Une petite bouchée de pain. Raphaël mâche tout doux. Dehors, une poule fait cot-cot. Tu as fini ta bouchée ? Oui, maman. Bravo. Une étape après l'autre. Le seau attend près des bottes.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6520,12 +6820,27 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Léa prend le seau bleu.
+          <t>narrateur|Raphaël prend le seau bleu.
+narrateur|Le seau fait un petit bruit de fer.
 maman|D'abord on déjeune.
-narrateur|Léa pose le seau. Elle mange une bouchée. Une étape après l'autre. On entend une poule.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+narrateur|Raphaël pose le seau près de la porte.
+narrateur|Il s'assoit à la table de bois.
+narrateur|Le lait est chaud dans le bol.
+papa|Une petite bouchée de pain.
+narrateur|Raphaël mâche tout doux.
+narrateur|Dehors, une poule fait cot-cot.
+maman|Tu as fini ta bouchée ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le seau attend près des bottes.</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>seau,poule</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6550,7 +6865,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>On fait tout en même temps ?</t>
+          <t>On fait une étape, puis l'autre ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6706,7 +7021,7 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|On fait tout en même temps ?</t>
+          <t>narrateur|On fait une étape, puis l'autre ?</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr"/>
@@ -6734,7 +7049,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Une étape après l'autre. Léa retient le geste. Maman sourit. On fait une étape après l'autre.</t>
+          <t>Oui. Une étape après l'autre. Raphaël pose les mains sur la table. Bravo. Tu as écouté l'étape. On fait l'étape dite. L'étape dite.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6878,7 +7193,13 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Une étape après l'autre. Léa retient le geste. Maman sourit. On fait une étape après l'autre.</t>
+          <t>narrateur|Oui.
+papa|Une étape après l'autre.
+narrateur|Raphaël pose les mains sur la table.
+maman|Bravo.
+maman|Tu as écouté l'étape.
+papa|On fait l'étape dite.
+enfant-m|L'étape dite.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6906,7 +7227,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va voir qui ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7074,7 +7395,8 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va voir qui ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7102,7 +7424,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le seau. Elle suit Tom vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Je suis là. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le seau. Le chat dort dans la paille. D'abord on se lave les mains. L'eau est tiède, un peu savon. Ensuite, on dit bonjour au chat. Raphaël caresse le chat, tout doux. Le poil est chaud. Il ronronne. Tu as lavé tes mains ? Oui, papa. Bravo. Une étape après l'autre. Le seau attend à sa place.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7242,11 +7564,26 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le seau. Elle suit Tom vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide.
-maman|Je suis là. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le seau.
+narrateur|Le chat dort dans la paille.
+papa|D'abord on se lave les mains.
+narrateur|L'eau est tiède, un peu savon.
+maman|Ensuite, on dit bonjour au chat.
+narrateur|Raphaël caresse le chat, tout doux.
+narrateur|Le poil est chaud.
+enfant-m|Il ronronne.
+papa|Tu as lavé tes mains ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le seau attend à sa place.</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>eau,chat</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7271,7 +7608,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7435,7 +7772,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7463,7 +7801,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le seau bleu. Puis Tom. Puis le matin. Un linge sèche à l'air. Léa souffle, puis sourit à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, le seau bleu sent l'eau fraîche. Le chat suit Raphaël. D'abord on pose le seau près du puits. Le seau fait un petit ding. Ensuite un peu d'eau pour le chat. Raphaël verse tout doux. Il lape. Bravo, Raphaël. Tu as fait l'étape dite. Une étape après l'autre. Ça sent le foin et le lait. Merci, papa.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7603,10 +7941,25 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le seau bleu. Puis Tom. Puis le matin. Un linge sèche à l'air. Léa souffle, puis sourit à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Le matin, le seau bleu sent l'eau fraîche.
+narrateur|Le chat suit Raphaël.
+papa|D'abord on pose le seau près du puits.
+narrateur|Le seau fait un petit ding.
+maman|Ensuite un peu d'eau pour le chat.
+narrateur|Raphaël verse tout doux.
+enfant-m|Il lape.
+papa|Bravo, Raphaël.
+papa|Tu as fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Ça sent le foin et le lait.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7631,7 +7984,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7771,7 +8124,13 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chat.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7799,7 +8158,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Léa s'arrête près de après la sieste. Tom est rangé. Le sol est un peu froid. Léa pose Tom à sa place. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le seau bleu est à l'ombre. Le chat s'étire sur le banc. D'abord on range le seau. Raphaël le pose contre le mur. Ensuite on caresse le chat. Le poil est chaud, tout soyeux. Tu as rangé le seau ? Oui, maman. Bravo. Une étape après l'autre. Un linge sèche à l'air. Merci, maman.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7939,10 +8298,25 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le sol est un peu froid. Léa pose Tom à sa place. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le seau bleu est à l'ombre.
+narrateur|Le chat s'étire sur le banc.
+maman|D'abord on range le seau.
+narrateur|Raphaël le pose contre le mur.
+papa|Ensuite on caresse le chat.
+narrateur|Le poil est chaud, tout soyeux.
+maman|Tu as rangé le seau ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+narrateur|Un linge sèche à l'air.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7967,7 +8341,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8107,7 +8481,13 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chat.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8135,7 +8515,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Léa se souvient de le seau bleu. Et de Tom. Et de le soir. Ça sent le pain chaud. J'ai appris. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, le seau bleu brille un peu. Le chat se couche près du poêle. D'abord le seau à sa place. Raphaël le pousse tout doux contre le mur. Ensuite les chaussons. Raphaël enfile les chaussons, un, puis deux. Tu as fait l'étape dite ? Oui. Bravo, mon grand. Une étape après l'autre. Merci, papa.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8275,12 +8655,24 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Léa se souvient de le seau bleu. Et de Tom. Et de le soir. Ça sent le pain chaud.
-enfant-f|J'ai appris. On fait une étape après l'autre. On fait l'étape dite.
-narrateur|Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|Le soir, le seau bleu brille un peu.
+narrateur|Le chat se couche près du poêle.
+papa|D'abord le seau à sa place.
+narrateur|Raphaël le pousse tout doux contre le mur.
+maman|Ensuite les chaussons.
+narrateur|Raphaël enfile les chaussons, un, puis deux.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui.
+maman|Bravo, mon grand.
+maman|Une étape après l'autre.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8305,7 +8697,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8445,7 +8837,13 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chat.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8473,7 +8871,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le seau. Elle suit son amie Léa vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman reste tout près. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le seau. Le chien attend près de l'étable. D'abord les bottes. Raphaël enfile la botte gauche. Puis la botte droite. Ensuite, on dit bonjour au chien. Le chien remue la queue. Wouaf, tout doux. Tu as mis tes bottes ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Le seau reste près de la porte.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8613,10 +9011,26 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le seau. Elle suit son amie Léa vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman reste tout près. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le seau.
+narrateur|Le chien attend près de l'étable.
+papa|D'abord les bottes.
+narrateur|Raphaël enfile la botte gauche.
+narrateur|Puis la botte droite.
+maman|Ensuite, on dit bonjour au chien.
+narrateur|Le chien remue la queue.
+enfant-m|Wouaf, tout doux.
+papa|Tu as mis tes bottes ?
+enfant-m|Oui, papa.
+papa|Bravo, Raphaël.
+papa|Une étape après l'autre.
+narrateur|Le seau reste près de la porte.</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>bottes,chien</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8641,7 +9055,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8805,7 +9219,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8833,7 +9248,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le seau bleu. Léa s'arrête. On attend son tour. Léa dit merci à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, le chien attend près du seau bleu. Raphaël tient l'anse, tout fort. D'abord on pose le seau. Le seau touche la terre, tout léger. Ensuite l'eau du chien. L'eau tremble dans le seau. Il a soif. Bravo. Tu as fait l'étape dite. Une étape après l'autre. Les bottes sont encore mouillées de rosée. Merci, maman.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8973,10 +9388,25 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le seau bleu. Léa s'arrête. On attend son tour. Léa dit merci à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Le matin, le chien attend près du seau bleu.
+narrateur|Raphaël tient l'anse, tout fort.
+maman|D'abord on pose le seau.
+narrateur|Le seau touche la terre, tout léger.
+papa|Ensuite l'eau du chien.
+narrateur|L'eau tremble dans le seau.
+enfant-m|Il a soif.
+maman|Bravo.
+maman|Tu as fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Les bottes sont encore mouillées de rosée.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9001,7 +9431,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9141,7 +9571,13 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chien.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9169,7 +9605,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Léa range Léa. après la sieste reste près de le seau bleu. Une chaussette est encore sablée. Léa sourit. Maman sourit aussi. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le chien bâille. Le seau bleu est près de l'étable. D'abord on range le seau. Raphaël le met contre la porte. Ensuite on dit merci au chien. Raphaël pose la main sur le dos chaud. Tu as rangé le seau ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Une feuille tombe, tout lentement. Merci, papa.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9309,10 +9745,25 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Léa range Léa. après la sieste reste près de le seau bleu. Une chaussette est encore sablée. Léa sourit. Maman sourit aussi. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le chien bâille.
+narrateur|Le seau bleu est près de l'étable.
+papa|D'abord on range le seau.
+narrateur|Raphaël le met contre la porte.
+maman|Ensuite on dit merci au chien.
+narrateur|Raphaël pose la main sur le dos chaud.
+papa|Tu as rangé le seau ?
+enfant-m|Oui, papa.
+maman|Bravo, Raphaël.
+maman|Une étape après l'autre.
+narrateur|Une feuille tombe, tout lentement.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9337,7 +9788,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9477,7 +9928,13 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chien.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9505,7 +9962,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, le chien rentre avec Raphaël. Le seau bleu est vide, tout léger. D'abord le seau près des bottes. Raphaël le pose. Ça fait un petit bruit. Ensuite on essuie les mains. Le linge sent le savon. Tu as fait l'étape dite ? Oui, maman. Bravo. Une étape après l'autre. Merci, maman.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9645,10 +10102,24 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le seau bleu reste dans le souvenir. Un ruban reste dans la poche. Léa ferme le sac. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|Le soir, le chien rentre avec Raphaël.
+narrateur|Le seau bleu est vide, tout léger.
+maman|D'abord le seau près des bottes.
+narrateur|Raphaël le pose. Ça fait un petit bruit.
+papa|Ensuite on essuie les mains.
+narrateur|Le linge sent le savon.
+maman|Tu as fait l'étape dite ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9673,7 +10144,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9813,7 +10284,13 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chien.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9841,7 +10318,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le seau. Elle suit Sami vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le seau. La poule picore dans la cour. D'abord le manteau. Raphaël passe un bras, puis l'autre. Ensuite, on va voir la poule. La poule fait cot-cot. Cot-cot. Tu as mis ton manteau ? Oui, maman. Bravo. Une étape après l'autre. Le seau reste sur le banc.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9981,10 +10458,25 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le seau. Elle suit Sami vers l'étable. Une étape après l'autre : d'abord les bottes. Papa aide. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le seau.
+narrateur|La poule picore dans la cour.
+maman|D'abord le manteau.
+narrateur|Raphaël passe un bras, puis l'autre.
+papa|Ensuite, on va voir la poule.
+narrateur|La poule fait cot-cot.
+enfant-m|Cot-cot.
+maman|Tu as mis ton manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le seau reste sur le banc.</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>manteau,poule</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10009,7 +10501,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10173,7 +10665,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10201,7 +10694,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le matin. Sami est rangé. le seau bleu est fini. L'eau coule, tout petit bruit. Léa raccroche un linge. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, Raphaël porte le seau bleu. La poule marche derrière, cot-cot. D'abord le seau près du poulailler. Raphaël le pose dans l'herbe. Ensuite un peu d'eau pour la poule. L'eau brille au soleil. Elle boit. Bravo, Raphaël. Tu as fait l'étape dite. Une étape après l'autre. Ça sent le grain et l'herbe. Merci, papa.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10341,10 +10834,25 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le matin. Sami est rangé. le seau bleu est fini. L'eau coule, tout petit bruit. Léa raccroche un linge. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Le matin, Raphaël porte le seau bleu.
+narrateur|La poule marche derrière, cot-cot.
+papa|D'abord le seau près du poulailler.
+narrateur|Raphaël le pose dans l'herbe.
+maman|Ensuite un peu d'eau pour la poule.
+narrateur|L'eau brille au soleil.
+enfant-m|Elle boit.
+papa|Bravo, Raphaël.
+papa|Tu as fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Ça sent le grain et l'herbe.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10369,7 +10877,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10509,7 +11017,13 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec la poule.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10537,7 +11051,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Léa pose Sami. le seau bleu est derrière. Le vent est doux. Léa montre après la sieste à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le seau bleu est tiède. La poule picore près des chaussures. D'abord on range le seau. Raphaël le met sous le banc. Ensuite on écoute la poule. Cot-cot, tout près. Tu as rangé le seau ? Oui. Bravo. Une étape après l'autre. Un linge claque un peu au vent. Merci, maman.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10677,10 +11191,25 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Léa pose Sami. le seau bleu est derrière. Le vent est doux. Léa montre après la sieste à maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le seau bleu est tiède.
+narrateur|La poule picore près des chaussures.
+maman|D'abord on range le seau.
+narrateur|Raphaël le met sous le banc.
+papa|Ensuite on écoute la poule.
+narrateur|Cot-cot, tout près.
+maman|Tu as rangé le seau ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Une étape après l'autre.
+narrateur|Un linge claque un peu au vent.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10705,7 +11234,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10845,7 +11374,13 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec la poule.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10873,7 +11408,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Léa montre le soir. Maman a vu le seau bleu. Et Sami. Les chaussures font toc toc. Léa ferme la porte, tout doux. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, Raphaël ramène le seau bleu. La poule est déjà au poulailler. D'abord le seau à sa place. Raphaël le pousse contre le mur de bois. Ensuite on ferme le petit volet. Clac, tout doux. Tu as fait l'étape dite ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Merci, papa.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11013,10 +11548,24 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Léa montre le soir. Maman a vu le seau bleu. Et Sami. Les chaussures font toc toc. Léa ferme la porte, tout doux. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|Le soir, Raphaël ramène le seau bleu.
+narrateur|La poule est déjà au poulailler.
+papa|D'abord le seau à sa place.
+narrateur|Raphaël le pousse contre le mur de bois.
+maman|Ensuite on ferme le petit volet.
+narrateur|Clac, tout doux.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui, papa.
+maman|Bravo, Raphaël.
+maman|Une étape après l'autre.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11041,7 +11590,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11181,7 +11730,13 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec la poule.
+narrateur|Il a posé le seau bleu, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11209,7 +11764,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Léa prend le doudou. D'abord on prépare le sac. Léa pose le doudou. Elle met le gobelet. Une étape après l'autre. Ensuite, le doudou.</t>
+          <t>Raphaël prend le doudou. Le doudou est doux contre sa joue. D'abord on prépare le sac. Raphaël pose le doudou sur le banc. Il met le gobelet dans le sac. Ensuite, le doudou. Raphaël glisse le doudou dans le sac. Tu as mis le gobelet ? Oui. Et le doudou. Bravo, Raphaël. Une étape après l'autre. Le sac tient bien droit. Raphaël pose une main dessus.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11349,13 +11904,26 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Léa prend le doudou.
+          <t>narrateur|Raphaël prend le doudou.
+narrateur|Le doudou est doux contre sa joue.
 maman|D'abord on prépare le sac.
-narrateur|Léa pose le doudou. Elle met le gobelet. Une étape après l'autre.
-papa|Ensuite, le doudou.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+narrateur|Raphaël pose le doudou sur le banc.
+narrateur|Il met le gobelet dans le sac.
+papa|Ensuite, le doudou.
+narrateur|Raphaël glisse le doudou dans le sac.
+maman|Tu as mis le gobelet ?
+enfant-m|Oui. Et le doudou.
+papa|Bravo, Raphaël.
+papa|Une étape après l'autre.
+narrateur|Le sac tient bien droit.
+narrateur|Raphaël pose une main dessus.</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>sac</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11568,7 +12136,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Une étape après l'autre. Léa hoche la tête. On continue, avec maman. On fait une étape après l'autre.</t>
+          <t>Oui. Maintenant, l'étape suivante. Une étape après l'autre. Bravo, Raphaël. Raphaël hoche la tête. Je suis prêt.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11712,7 +12280,12 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Une étape après l'autre. Léa hoche la tête. On continue, avec maman. On fait une étape après l'autre.</t>
+          <t>narrateur|Oui.
+maman|Maintenant, l'étape suivante.
+maman|Une étape après l'autre.
+papa|Bravo, Raphaël.
+narrateur|Raphaël hoche la tête.
+enfant-m|Je suis prêt.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11740,7 +12313,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre Tom, Léa, ou Sami.</t>
+          <t>On va voir qui ? Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11908,7 +12481,8 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre Tom, Léa, ou Sami.</t>
+          <t>narrateur|On va voir qui ?
+papa|Le chat, le chien, ou la poule.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11936,7 +12510,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le doudou. Avec Tom, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman reste tout près. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le doudou. Le chat dort dans la paille. D'abord on se lave les mains. L'eau est tiède, un peu savon. Ensuite, on dit bonjour au chat. Raphaël caresse le chat, tout doux. Le poil est chaud. Il ronronne. Tu as lavé tes mains ? Oui, papa. Bravo. Une étape après l'autre. Le doudou attend à sa place.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12076,10 +12650,26 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le doudou. Avec Tom, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman reste tout près. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le doudou.
+narrateur|Le chat dort dans la paille.
+papa|D'abord on se lave les mains.
+narrateur|L'eau est tiède, un peu savon.
+maman|Ensuite, on dit bonjour au chat.
+narrateur|Raphaël caresse le chat, tout doux.
+narrateur|Le poil est chaud.
+enfant-m|Il ronronne.
+papa|Tu as lavé tes mains ?
+enfant-m|Oui, papa.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le doudou attend à sa place.</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>eau,chat</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12104,7 +12694,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12268,7 +12858,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12296,7 +12887,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Léa a choisi le doudou. Puis Tom. Puis le matin. On entend un oiseau. Léa range encore un peu, près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, le doudou sent encore le lit. Le chat se frotte contre le sac. D'abord le doudou dans le sac. Raphaël le glisse, tout doux. Ensuite on dit bonjour au chat. Raphaël caresse, une fois, tout lentement. Il ronronne. Bravo. Tu as fait l'étape dite. Une étape après l'autre. Le sac est prêt près de la porte. Merci, maman.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12436,10 +13027,25 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Léa a choisi le doudou. Puis Tom. Puis le matin. On entend un oiseau. Léa range encore un peu, près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Le matin, le doudou sent encore le lit.
+narrateur|Le chat se frotte contre le sac.
+maman|D'abord le doudou dans le sac.
+narrateur|Raphaël le glisse, tout doux.
+papa|Ensuite on dit bonjour au chat.
+narrateur|Raphaël caresse, une fois, tout lentement.
+enfant-m|Il ronronne.
+maman|Bravo.
+maman|Tu as fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Le sac est prêt près de la porte.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12464,7 +13070,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12604,7 +13210,13 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chat.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12632,7 +13244,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Léa s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Papa n'est pas loin. Léa les rejoint. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le doudou est chaud. Le chat dort au pied du lit. D'abord on pose le doudou sur l'oreiller. Raphaël le lisse avec la main. Ensuite on range le sac. Le sac va contre la chaise. Tu as posé le doudou ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. La couverture est douce. Merci, papa.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12772,10 +13384,25 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Léa s'arrête près de après la sieste. Tom est rangé. Le savon sent bon. Papa n'est pas loin. Léa les rejoint. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le doudou est chaud.
+narrateur|Le chat dort au pied du lit.
+papa|D'abord on pose le doudou sur l'oreiller.
+narrateur|Raphaël le lisse avec la main.
+maman|Ensuite on range le sac.
+narrateur|Le sac va contre la chaise.
+papa|Tu as posé le doudou ?
+enfant-m|Oui, papa.
+maman|Bravo, Raphaël.
+maman|Une étape après l'autre.
+narrateur|La couverture est douce.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12800,7 +13427,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12940,7 +13567,13 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chat.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12968,7 +13601,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Léa se souvient de le doudou. Et de Tom. Et de le soir. On dit merci. Léa répète tout bas le geste. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, Raphaël tient le doudou. Le chat saute sur le lit, tout léger. D'abord le doudou sous la joue. Raphaël s'allonge un peu. Ensuite on éteint la grande lumière. Il reste une petite lampe. Tu as fait l'étape dite ? Oui, maman. Bravo. Une étape après l'autre. Merci, maman.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13108,10 +13741,24 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Léa se souvient de le doudou. Et de Tom. Et de le soir. On dit merci. Léa répète tout bas le geste. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|Le soir, Raphaël tient le doudou.
+narrateur|Le chat saute sur le lit, tout léger.
+maman|D'abord le doudou sous la joue.
+narrateur|Raphaël s'allonge un peu.
+papa|Ensuite on éteint la grande lumière.
+narrateur|Il reste une petite lampe.
+maman|Tu as fait l'étape dite ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13136,7 +13783,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13276,7 +13923,13 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chat.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13304,7 +13957,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le doudou. Avec son amie Léa, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le doudou. Le chien attend près de l'étable. D'abord les bottes. Raphaël enfile la botte gauche. Puis la botte droite. Ensuite, on dit bonjour au chien. Le chien remue la queue. Wouaf, tout doux. Tu as mis tes bottes ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Le doudou reste près de la porte.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13444,10 +14097,26 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le doudou. Avec son amie Léa, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Maman montre le geste, lentement. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le doudou.
+narrateur|Le chien attend près de l'étable.
+papa|D'abord les bottes.
+narrateur|Raphaël enfile la botte gauche.
+narrateur|Puis la botte droite.
+maman|Ensuite, on dit bonjour au chien.
+narrateur|Le chien remue la queue.
+enfant-m|Wouaf, tout doux.
+papa|Tu as mis tes bottes ?
+enfant-m|Oui, papa.
+papa|Bravo, Raphaël.
+papa|Une étape après l'autre.
+narrateur|Le doudou reste près de la porte.</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>bottes,chien</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13472,7 +14141,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13636,7 +14305,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13664,7 +14334,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Avec le matin. Après Léa. Près de le doudou. Léa s'arrête. Un chat miaule une fois. Léa tend le matin à papa. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, le doudou dépasse du sac. Le chien attend près des bottes. D'abord le doudou bien dans le sac. Raphaël le rentre, tout doux. Ensuite on dit bonjour au chien. Le chien pose le museau sur la main. Il est chaud. Bravo, Raphaël. Tu as fait l'étape dite. Une étape après l'autre. Les bottes sont prêtes. Merci, papa.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13804,10 +14474,25 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Avec le matin. Après Léa. Près de le doudou. Léa s'arrête. Un chat miaule une fois. Léa tend le matin à papa. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Le matin, le doudou dépasse du sac.
+narrateur|Le chien attend près des bottes.
+papa|D'abord le doudou bien dans le sac.
+narrateur|Raphaël le rentre, tout doux.
+maman|Ensuite on dit bonjour au chien.
+narrateur|Le chien pose le museau sur la main.
+enfant-m|Il est chaud.
+papa|Bravo, Raphaël.
+papa|Tu as fait l'étape dite.
+maman|Une étape après l'autre.
+narrateur|Les bottes sont prêtes.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13832,7 +14517,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13972,7 +14657,13 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec le chien.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -14000,7 +14691,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Léa range Léa. après la sieste reste près de le doudou. Il y a des miettes sur la table. Léa marche près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le doudou sent le soleil. Le chien est couché dans la cour. D'abord on pose le doudou sur le banc. Raphaël le plie un peu. Ensuite on rejoint le chien, tout calme. Raphaël s'assoit près de papa. Tu as posé le doudou ? Oui. Bravo. Une étape après l'autre. Le vent est doux. Merci, maman.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14140,10 +14831,25 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Léa range Léa. après la sieste reste près de le doudou. Il y a des miettes sur la table. Léa marche près de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le doudou sent le soleil.
+narrateur|Le chien est couché dans la cour.
+maman|D'abord on pose le doudou sur le banc.
+narrateur|Raphaël le plie un peu.
+papa|Ensuite on rejoint le chien, tout calme.
+narrateur|Raphaël s'assoit près de papa.
+maman|Tu as posé le doudou ?
+enfant-m|Oui.
+papa|Bravo.
+papa|Une étape après l'autre.
+narrateur|Le vent est doux.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14168,7 +14874,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14308,7 +15014,13 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec le chien.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14336,7 +15048,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, Raphaël serre le doudou. Le chien se couche près de la porte. D'abord le doudou dans le lit. Raphaël le pose sur l'oreiller. Ensuite on dit bonne nuit au chien. Raphaël chuchote, tout bas. Tu as fait l'étape dite ? Oui, papa. Bravo, mon grand. Une étape après l'autre. Merci, papa.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14476,10 +15188,24 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Le soir est là. Léa aussi. le doudou reste dans le souvenir. On souffle doucement. Léa serre la main de maman. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|Le soir, Raphaël serre le doudou.
+narrateur|Le chien se couche près de la porte.
+papa|D'abord le doudou dans le lit.
+narrateur|Raphaël le pose sur l'oreiller.
+maman|Ensuite on dit bonne nuit au chien.
+narrateur|Raphaël chuchote, tout bas.
+papa|Tu as fait l'étape dite ?
+enfant-m|Oui, papa.
+maman|Bravo, mon grand.
+maman|Une étape après l'autre.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14504,7 +15230,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14644,7 +15370,13 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec le chien.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14672,7 +15404,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa a posé le doudou. Avec Sami, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou. Je suis là. On fait une étape après l'autre.</t>
+          <t>Raphaël a posé le doudou. La poule picore dans la cour. D'abord le manteau. Raphaël passe un bras, puis l'autre. Ensuite, on va voir la poule. La poule fait cot-cot. Cot-cot. Tu as mis ton manteau ? Oui, maman. Bravo. Une étape après l'autre. Le doudou reste sur le banc.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14812,11 +15544,25 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Léa a posé le doudou. Avec Sami, elle attend. Une étape après l'autre : d'abord le manteau, ensuite le doudou.
-maman|Je suis là. On fait une étape après l'autre.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Raphaël a posé le doudou.
+narrateur|La poule picore dans la cour.
+maman|D'abord le manteau.
+narrateur|Raphaël passe un bras, puis l'autre.
+papa|Ensuite, on va voir la poule.
+narrateur|La poule fait cot-cot.
+enfant-m|Cot-cot.
+maman|Tu as mis ton manteau ?
+enfant-m|Oui, maman.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le doudou reste sur le banc.</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>manteau,poule</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14841,7 +15587,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment ? Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15005,7 +15751,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>narrateur|C'est quel moment ?
+maman|Le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15033,7 +15780,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Léa rejoint le matin. Sami est rangé. le doudou est fini. Une feuille tombe. Léa chuchote : c'est fini. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le matin, le doudou est dans le sac. La poule picore près des chaussures. D'abord on ferme le sac. Raphaël tire la fermeture, tout doux. Ensuite on va voir la poule. Raphaël reste près de maman. Cot-cot. Bravo. Tu as fait l'étape dite. Une étape après l'autre. Le sac est prêt. Merci, maman.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15173,10 +15920,25 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Léa rejoint le matin. Sami est rangé. le doudou est fini. Une feuille tombe. Léa chuchote : c'est fini. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Le matin, le doudou est dans le sac.
+narrateur|La poule picore près des chaussures.
+maman|D'abord on ferme le sac.
+narrateur|Raphaël tire la fermeture, tout doux.
+papa|Ensuite on va voir la poule.
+narrateur|Raphaël reste près de maman.
+enfant-m|Cot-cot.
+maman|Bravo.
+maman|Tu as fait l'étape dite.
+papa|Une étape après l'autre.
+narrateur|Le sac est prêt.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>coq,paille</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15201,7 +15963,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15341,7 +16103,13 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le matin, avec la poule.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15369,7 +16137,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Près de après la sieste. Léa pose Sami. le doudou est derrière. Un galet est encore chaud. Léa écoute maman encore une fois. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Après la sieste, le doudou est un peu chaud. La poule se tient dans l'herbe. D'abord le doudou sur l'oreiller. Raphaël le lisse. Ensuite on ouvre un peu le volet. La lumière revient, tout douce. Tu as posé le doudou ? Oui, papa. Bravo, Raphaël. Une étape après l'autre. Merci, papa.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15509,10 +16277,24 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Près de après la sieste. Léa pose Sami. le doudou est derrière. Un galet est encore chaud. Léa écoute maman encore une fois. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|Après la sieste, le doudou est un peu chaud.
+narrateur|La poule se tient dans l'herbe.
+papa|D'abord le doudou sur l'oreiller.
+narrateur|Raphaël le lisse.
+maman|Ensuite on ouvre un peu le volet.
+narrateur|La lumière revient, tout douce.
+papa|Tu as posé le doudou ?
+enfant-m|Oui, papa.
+maman|Bravo, Raphaël.
+maman|Une étape après l'autre.
+enfant-m|Merci, papa.</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>couverture</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15537,7 +16319,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15677,7 +16459,13 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu après la sieste, avec la poule.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15705,7 +16493,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Léa montre le soir. Maman a vu le doudou. Et Sami. Une tasse cliquette. Léa range la tasse. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
+          <t>Le soir, Raphaël tient le doudou contre sa joue. La poule est au poulailler. D'abord le doudou dans le lit. Raphaël s'allonge un peu. Ensuite on ferme le volet, tout doux. La chambre devient sombre et calme. Tu as fait l'étape dite ? Oui, maman. Bravo. Une étape après l'autre. Merci, maman.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15845,10 +16633,24 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Léa montre le soir. Maman a vu le doudou. Et Sami. Une tasse cliquette. Léa range la tasse. On fait une étape après l'autre. On fait l'étape dite. Une étape après l'autre. Léa dit merci à maman.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|Le soir, Raphaël tient le doudou contre sa joue.
+narrateur|La poule est au poulailler.
+maman|D'abord le doudou dans le lit.
+narrateur|Raphaël s'allonge un peu.
+papa|Ensuite on ferme le volet, tout doux.
+narrateur|La chambre devient sombre et calme.
+maman|Tu as fait l'étape dite ?
+enfant-m|Oui, maman.
+papa|Bravo.
+papa|Une étape après l'autre.
+enfant-m|Merci, maman.</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>porte</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15873,7 +16675,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16013,7 +16815,13 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Raphaël a vécu le soir, avec la poule.
+narrateur|Il a posé le doudou, à sa place.
+maman|Bravo, Raphaël.
+maman|Tu as fait du bon travail.
+papa|Une étape après l'autre.
+enfant-m|Une étape après l'autre.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16035,7 +16843,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16087,6 +16895,13 @@
       <c r="A7" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-005.xlsx
+++ b/stories/arbres/TREE-AUT-005.xlsx
@@ -1197,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Un coq chante derrière la grange. L'herbe brille, encore mouillée. La petite maison sent le foin chaud. Un volet bleu bouge tout doux. Les bottes de papa attendent près de la porte. Dans la cuisine, le lait fume. Le lait est prêt, Raphaël. Tu as entendu le coq ? Oui, papa. Le bois du plancher est un peu froid. Un rayon pose une barre jaune. En ce moment, Raphaël est dans la cuisine. Il tient son doudou contre sa joue. Il a envie d'aller voir les bêtes. D'abord on s'habille. Ensuite on déjeune. Une étape après l'autre, mon grand. Une étape après l'autre. Raphaël hoche la tête. Tu es prêt ? Oui, maman.</t>
+          <t>Un coq chante derrière la grange. L'herbe brille, encore mouillée. La petite maison sent le foin chaud. Un volet bleu bouge tout doux. Les bottes de papa attendent près de la porte. Dans la cuisine, le lait fume. Le lait est prêt, Raphaël. Tu as entendu le coq ? Oui, papa. Le bois du plancher est un peu froid. Un rayon pose une barre jaune. En ce moment, Raphaël est dans la cuisine. Il tient son doudou contre sa joue. Il a envie d'aller voir les bêtes. D'abord on s'habille. Ensuite on déjeune. Une étape après l'autre, mon grand. Une étape après l'autre. Raphaël hoche la tête. Tu as froid aux pieds ? Un peu. On met les chaussons d'abord. Raphaël glisse les pieds dans les chaussons. Une paille dépasse d'une botte. La table de bois est encore un peu froide. Ça sent le lait et le foin. Bravo. Une étape après l'autre. Le coq chante encore, plus loin. Tu es prêt ? Oui, maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1356,6 +1356,16 @@
 maman|Une étape après l'autre, mon grand.
 enfant-m|Une étape après l'autre.
 narrateur|Raphaël hoche la tête.
+maman|Tu as froid aux pieds ?
+enfant-m|Un peu.
+papa|On met les chaussons d'abord.
+narrateur|Raphaël glisse les pieds dans les chaussons.
+narrateur|Une paille dépasse d'une botte.
+narrateur|La table de bois est encore un peu froide.
+narrateur|Ça sent le lait et le foin.
+maman|Bravo.
+maman|Une étape après l'autre.
+narrateur|Le coq chante encore, plus loin.
 maman|Tu es prêt ?
 enfant-m|Oui, maman.</t>
         </is>
@@ -2893,7 +2903,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3037,6 +3047,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -3251,7 +3262,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3395,6 +3406,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -3609,7 +3621,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3753,6 +3765,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -4344,7 +4357,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4488,6 +4501,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -4702,7 +4716,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4846,6 +4860,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -5059,7 +5074,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5203,6 +5218,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -5792,7 +5808,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5936,6 +5952,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -6149,7 +6166,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6293,6 +6310,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -6506,7 +6524,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le ballon rouge, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6650,6 +6668,7 @@
 narrateur|Il a posé le ballon rouge, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -7984,7 +8003,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8128,6 +8147,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -8341,7 +8361,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8485,6 +8505,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -8697,7 +8718,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8841,6 +8862,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -9431,7 +9453,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9575,6 +9597,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -9788,7 +9811,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9932,6 +9955,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -10144,7 +10168,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10288,6 +10312,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -10877,7 +10902,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -11021,6 +11046,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -11234,7 +11260,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11378,6 +11404,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -11590,7 +11617,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le seau bleu, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11734,6 +11761,7 @@
 narrateur|Il a posé le seau bleu, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -13070,7 +13098,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13214,6 +13242,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -13427,7 +13456,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13571,6 +13600,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -13783,7 +13813,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chat. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13927,6 +13957,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -14517,7 +14548,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14661,6 +14692,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -14874,7 +14906,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -15018,6 +15050,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -15230,7 +15263,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec le chien. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15374,6 +15407,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -15963,7 +15997,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le matin, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le matin, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -16107,6 +16141,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -16319,7 +16354,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu après la sieste, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16463,6 +16498,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -16675,7 +16711,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a vécu le soir, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
+          <t>Raphaël a vécu le soir, avec la poule. Il a posé le doudou, à sa place. Bravo, Raphaël. Tu as fait du bon travail. Tu as fait l'étape dite. Une étape après l'autre. Une étape après l'autre. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16819,6 +16855,7 @@
 narrateur|Il a posé le doudou, à sa place.
 maman|Bravo, Raphaël.
 maman|Tu as fait du bon travail.
+papa|Tu as fait l'étape dite.
 papa|Une étape après l'autre.
 enfant-m|Une étape après l'autre.
 narrateur|L'histoire est finie.</t>
@@ -16843,7 +16880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16900,6 +16937,13 @@
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>

--- a/stories/arbres/TREE-AUT-005.xlsx
+++ b/stories/arbres/TREE-AUT-005.xlsx
@@ -854,7 +854,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Après la pluie, à la ferme, le volet bleu tape toc. Le coq a chanté une fois derrière la grange, puis s'est tu. Raphaël veut le rejoindre tout de suite, ballon, seau de grain ou doudou à la main. Pieds nus, la pierre mouillée le pique : il met la botte gauche, puis la droite. Sur le chemin, chat, chien ou poule font autre chose que prévu. La première idée rate. L'animal montre trois coins : le secret du cabanon, le fournil, les tomates. Raphaël comprend sans forcer le coq. Le toc du loquet paie le volet. Les bottes gardent boue et paille.</t>
+          <t>Après la pluie, à la ferme, le volet bleu tape toc. Le coq a chanté une fois derrière la grange, puis s'est tu. Raphaël veut le rejoindre vite, ballon, seau de grain ou doudou à la main. Pieds nus, la pierre mouillée le pique : il met la botte gauche, puis la droite. Sur le chemin, chat, chien ou poule font autre chose que prévu. La première idée rate. L'animal montre trois coins : le secret du cabanon, le fournil, les tomates. Raphaël comprend sans forcer le coq. Le toc du loquet paie le volet. Les bottes gardent boue et paille.</t>
         </is>
       </c>
     </row>
@@ -1803,7 +1803,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes</t>
+          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes | les bottes de Raphaël</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       <c r="L9" s="2" t="inlineStr"/>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2587,7 +2587,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr"/>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Le fournil sent le pain, tout chaud.
+          <t>narrateur|Le fournil sent le pain, bien chaud.
 narrateur|De la farine flotte, blanche, légère.
 narrateur|Le chat éternue, et saute d'un sac.
 enfant-m|Le coq est sur la planche !
@@ -4100,7 +4100,7 @@
       <c r="L17" s="2" t="inlineStr"/>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4120,7 +4120,7 @@
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
@@ -5622,7 +5622,7 @@
       <c r="L25" s="2" t="inlineStr"/>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -5632,7 +5632,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
@@ -6168,17 +6168,17 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le ballon rouge sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr"/>
@@ -6317,7 +6317,7 @@
 enfant-m|Coq, viens, c'est bon ici !
 narrateur|Raphaël tape des mains, trop fort.
 narrateur|La farine saute, et le coq cligne.
-enfant-m|Il se ferme, tout petit.
+enfant-m|Il se ferme, très petit.
 maman|Plus de mains, la pierre suffit.
 narrateur|La poule picore, sans bruit, maintenant.
 narrateur|Le coq baisse une aile, moins dur.
@@ -7136,7 +7136,7 @@
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes</t>
+          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes | les bottes de Raphaël</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -7905,7 +7905,7 @@
       <c r="L37" s="2" t="inlineStr"/>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -7915,7 +7915,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -7925,7 +7925,7 @@
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
@@ -8451,17 +8451,17 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr"/>
@@ -8595,7 +8595,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Le fournil sent le pain, tout chaud.
+          <t>narrateur|Le fournil sent le pain, bien chaud.
 narrateur|De la farine flotte, blanche, légère.
 narrateur|Le chat éternue, et saute d'un sac.
 enfant-m|Le coq est sur la planche !
@@ -9428,7 +9428,7 @@
       <c r="L45" s="2" t="inlineStr"/>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -9448,7 +9448,7 @@
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
@@ -10950,7 +10950,7 @@
       <c r="L53" s="2" t="inlineStr"/>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -10960,7 +10960,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -10970,7 +10970,7 @@
       </c>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
@@ -11496,17 +11496,17 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le seau bleu sur la pierre tiède. Le dernier grain sonne, tout petit. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr"/>
@@ -11645,7 +11645,7 @@
 enfant-m|Coq, viens, c'est bon ici !
 narrateur|Raphaël tape des mains, trop fort.
 narrateur|La farine saute, et le coq cligne.
-enfant-m|Il se ferme, tout petit.
+enfant-m|Il se ferme, très petit.
 maman|Plus de mains, la pierre suffit.
 narrateur|La poule picore, sans bruit, maintenant.
 narrateur|Le coq baisse une aile, moins dur.
@@ -12464,7 +12464,7 @@
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes</t>
+          <t>les bottes | bottes | ses bottes | les bottes d'abord | mettre les bottes | les bottes de Raphaël</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr">
@@ -13236,7 +13236,7 @@
       <c r="L65" s="2" t="inlineStr"/>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N65" s="2" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -13256,7 +13256,7 @@
       </c>
       <c r="Q65" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R65" s="2" t="inlineStr">
@@ -13782,17 +13782,17 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le coq est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>Le fournil sent le pain, tout chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil sent le pain, bien chaud. De la farine flotte, blanche, légère. Le chat éternue, et saute d'un sac. Le &lt;emphasis&gt;coq&lt;/emphasis&gt; est sur la planche ! Raphaël tape des mains, pour l'appeler. Un nuage blanc cache tout, un moment. Je ne le vois plus. Plus de bruit, laisse la farine tomber. Le coq est là, plumes blanches. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr"/>
@@ -13926,7 +13926,7 @@
       </c>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Le fournil sent le pain, tout chaud.
+          <t>narrateur|Le fournil sent le pain, bien chaud.
 narrateur|De la farine flotte, blanche, légère.
 narrateur|Le chat éternue, et saute d'un sac.
 enfant-m|Le coq est sur la planche !
@@ -14758,7 +14758,7 @@
       <c r="L73" s="2" t="inlineStr"/>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -14778,7 +14778,7 @@
       </c>
       <c r="Q73" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R73" s="2" t="inlineStr">
@@ -16279,7 +16279,7 @@
       <c r="L81" s="2" t="inlineStr"/>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>le matin</t>
+          <t>le secret du cabanon</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -16289,7 +16289,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>après la sieste</t>
+          <t>le fournil</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -16299,7 +16299,7 @@
       </c>
       <c r="Q81" s="2" t="inlineStr">
         <is>
-          <t>le soir</t>
+          <t>les tomates</t>
         </is>
       </c>
       <c r="R81" s="2" t="inlineStr">
@@ -16825,17 +16825,17 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le coq cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
+          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis level="moderate"&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul.&lt;/prosody&gt;&lt;break time="560ms"/&gt;&lt;/speak&gt;</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, tout petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
+          <t>Le fournil a une pierre tiède, au bord. La poule picore la farine, chh. Coq, viens, c'est bon ici ! Raphaël tape des mains, trop fort. La farine saute, et le &lt;emphasis&gt;coq&lt;/emphasis&gt; cligne. Il se ferme, très petit. Plus de mains, la pierre suffit. La poule picore, sans bruit, maintenant. Le coq baisse une aile, moins dur. Raphaël pose le doudou sur la pierre. Un peu de grain, s'il en reste. Je ne te prends pas. Le coq descend, une patte, puis l'autre. La vapeur ressemble au lait du bol. Il est venu, tout seul. [pause]</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr"/>
@@ -16974,7 +16974,7 @@
 enfant-m|Coq, viens, c'est bon ici !
 narrateur|Raphaël tape des mains, trop fort.
 narrateur|La farine saute, et le coq cligne.
-enfant-m|Il se ferme, tout petit.
+enfant-m|Il se ferme, très petit.
 maman|Plus de mains, la pierre suffit.
 narrateur|La poule picore, sans bruit, maintenant.
 narrateur|Le coq baisse une aile, moins dur.
@@ -17575,7 +17575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -17653,6 +17653,13 @@
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
